--- a/output/yearly_surface_area_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_40_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634592827</v>
+        <v>10.844976181371</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907198969287</v>
+        <v>37.78907141629683</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.901285450227578</v>
+        <v>5.39863062565321</v>
       </c>
       <c r="C2" t="n">
-        <v>12.14421910153304</v>
+        <v>7.447538084416303</v>
       </c>
       <c r="D2" t="n">
-        <v>35.65020438431443</v>
+        <v>17.64789673154067</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.66578917439536</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C3" t="n">
-        <v>24.25407703341745</v>
+        <v>28.75048151886784</v>
       </c>
       <c r="D3" t="n">
-        <v>77.34208414056373</v>
+        <v>65.92435834017333</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.5216364927871</v>
+        <v>38.05843150283185</v>
       </c>
       <c r="C4" t="n">
-        <v>53.79486545420397</v>
+        <v>65.85563600087605</v>
       </c>
       <c r="D4" t="n">
-        <v>87.04175145852221</v>
+        <v>87.10556505929826</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.62734644967627</v>
+        <v>46.36303533305563</v>
       </c>
       <c r="C5" t="n">
-        <v>84.16032194655783</v>
+        <v>98.34657627292425</v>
       </c>
       <c r="D5" t="n">
-        <v>61.11379458936396</v>
+        <v>66.78338758138929</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.42274201656544</v>
+        <v>41.0164373357275</v>
       </c>
       <c r="C6" t="n">
-        <v>91.89453036061421</v>
+        <v>112.4631265122891</v>
       </c>
       <c r="D6" t="n">
-        <v>44.59883470852411</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.23139902522853</v>
+        <v>26.64954143177966</v>
       </c>
       <c r="C7" t="n">
-        <v>87.49433715017997</v>
+        <v>114.1438785819597</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>67.67677799225388</v>
+        <v>82.28027509292518</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>46.03905859065416</v>
       </c>
       <c r="D9" t="n">
         <v>34.05780960802609</v>
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.699327308446108</v>
+        <v>7.685704860481388</v>
       </c>
       <c r="C21" t="n">
-        <v>95.2791754420206</v>
+        <v>93.18917143333682</v>
       </c>
       <c r="D21" t="n">
-        <v>8.661743222001872</v>
+        <v>7.685704860481388</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.239407571115979</v>
+        <v>8.749335540247575</v>
       </c>
       <c r="C2" t="n">
-        <v>12.16090881250524</v>
+        <v>4.909720268938299</v>
       </c>
       <c r="D2" t="n">
-        <v>29.3306944120777</v>
+        <v>23.24778563656447</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.12582793705961</v>
+        <v>18.11815388187489</v>
       </c>
       <c r="C3" t="n">
-        <v>36.1823116400162</v>
+        <v>28.69157665661304</v>
       </c>
       <c r="D3" t="n">
-        <v>85.86365421342605</v>
+        <v>64.52536786162162</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.58995792145688</v>
+        <v>36.16954891986099</v>
       </c>
       <c r="C4" t="n">
-        <v>57.20251173564466</v>
+        <v>68.11463746834795</v>
       </c>
       <c r="D4" t="n">
-        <v>102.1655748424443</v>
+        <v>97.36679206408591</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.73243451175969</v>
+        <v>51.68901662859458</v>
       </c>
       <c r="C5" t="n">
-        <v>90.66440048719295</v>
+        <v>109.6121311791564</v>
       </c>
       <c r="D5" t="n">
-        <v>76.57632093125122</v>
+        <v>81.19053514121123</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>50.87809302488671</v>
       </c>
       <c r="C6" t="n">
-        <v>112.2216165770444</v>
+        <v>132.2669412023558</v>
       </c>
       <c r="D6" t="n">
-        <v>52.08564270111029</v>
+        <v>55.30577517103983</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.35223610830891</v>
+        <v>36.89015173477814</v>
       </c>
       <c r="C7" t="n">
-        <v>108.7540836856447</v>
+        <v>138.0386359556228</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.28906009787184</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>114.491417269263</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>62.01405723415825</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
         <v>35.44600086183109</v>
@@ -1223,7 +1223,7 @@
         <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.883899237873268</v>
+        <v>7.867498853733873</v>
       </c>
       <c r="C21" t="n">
-        <v>104.4616649018208</v>
+        <v>101.2940477418236</v>
       </c>
       <c r="D21" t="n">
-        <v>9.854874047341585</v>
+        <v>8.850936210450607</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.275552309723864</v>
+        <v>9.18130453011617</v>
       </c>
       <c r="C2" t="n">
-        <v>7.309111658117502</v>
+        <v>4.719261214314417</v>
       </c>
       <c r="D2" t="n">
-        <v>35.50588747179015</v>
+        <v>22.54092728950677</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.75062038758809</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="C3" t="n">
-        <v>41.26776474801468</v>
+        <v>23.90555659840983</v>
       </c>
       <c r="D3" t="n">
-        <v>88.00877294720533</v>
+        <v>66.91101478294136</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.2881604656256</v>
+        <v>34.66354794154638</v>
       </c>
       <c r="C4" t="n">
-        <v>72.64540312344698</v>
+        <v>68.90592611797088</v>
       </c>
       <c r="D4" t="n">
-        <v>117.6467543907123</v>
+        <v>105.2158649595392</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.01499792413352</v>
+        <v>52.47441479199203</v>
       </c>
       <c r="C5" t="n">
-        <v>96.26036240139979</v>
+        <v>116.5579961867026</v>
       </c>
       <c r="D5" t="n">
-        <v>90.76257525761763</v>
+        <v>93.19240082562848</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.56365602208724</v>
+        <v>58.72716592033996</v>
       </c>
       <c r="C6" t="n">
-        <v>126.591457724105</v>
+        <v>149.3738949488565</v>
       </c>
       <c r="D6" t="n">
-        <v>61.9472983902695</v>
+        <v>65.77120569831082</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.05386692167588</v>
+        <v>47.31042186765379</v>
       </c>
       <c r="C7" t="n">
-        <v>131.5708820800448</v>
+        <v>162.113053159163</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>48.20872101703962</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.80219535202343</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>143.7818600254666</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.07968579496001</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>85.31093025593505</v>
+        <v>102.2843663146582</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>54.6637121724624</v>
+        <v>61.06961594267285</v>
       </c>
       <c r="D10" t="n">
         <v>36.30012136452581</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.053133810668061</v>
+        <v>8.033940095816908</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7438733493529</v>
+        <v>109.4624338055053</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07305898966858</v>
+        <v>10.04242511977113</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.358599953957343</v>
+        <v>8.328165775125692</v>
       </c>
       <c r="C2" t="n">
-        <v>4.911683764346792</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="D2" t="n">
-        <v>29.08034874749477</v>
+        <v>18.54619588092649</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.44337441388784</v>
+        <v>25.96722677732814</v>
       </c>
       <c r="C3" t="n">
-        <v>55.55710258332701</v>
+        <v>36.65355053805467</v>
       </c>
       <c r="D3" t="n">
-        <v>94.57175635009526</v>
+        <v>73.70470889632928</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.38879745307752</v>
+        <v>25.20637230653686</v>
       </c>
       <c r="C4" t="n">
-        <v>88.49670155621598</v>
+        <v>96.54997797415255</v>
       </c>
       <c r="D4" t="n">
-        <v>110.0912240588288</v>
+        <v>102.7143718091183</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>33.08489763311751</v>
       </c>
       <c r="C5" t="n">
-        <v>75.64366061221675</v>
+        <v>89.24086631603508</v>
       </c>
       <c r="D5" t="n">
-        <v>62.26734814185396</v>
+        <v>65.23713494720056</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.77743067523902</v>
+        <v>29.34345713223292</v>
       </c>
       <c r="C6" t="n">
-        <v>86.66181509697871</v>
+        <v>106.7473913781642</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>31.71830482880595</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>80.6073770048886</v>
+        <v>101.0885976108856</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>62.83676181031709</v>
+        <v>75.35404503946393</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>46.59374604355361</v>
       </c>
       <c r="D9" t="n">
         <v>27.62343515439249</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
         <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.071708640139023</v>
+        <v>4.792892292132928</v>
       </c>
       <c r="C2" t="n">
-        <v>2.371902453460294</v>
+        <v>2.216786316189298</v>
       </c>
       <c r="D2" t="n">
-        <v>20.38500933098077</v>
+        <v>13.35471402086936</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.34796496012665</v>
+        <v>28.0387144332889</v>
       </c>
       <c r="C3" t="n">
-        <v>37.41440500884595</v>
+        <v>24.53878386764903</v>
       </c>
       <c r="D3" t="n">
-        <v>96.034560429423</v>
+        <v>72.04555527615217</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76488893926206</v>
+        <v>36.01639627799848</v>
       </c>
       <c r="C4" t="n">
-        <v>116.3704823751914</v>
+        <v>96.72865605632549</v>
       </c>
       <c r="D4" t="n">
-        <v>129.7075249373843</v>
+        <v>115.2090748410674</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.57072387799944</v>
+        <v>37.01188845010476</v>
       </c>
       <c r="C5" t="n">
-        <v>115.9934912567607</v>
+        <v>132.3886779176824</v>
       </c>
       <c r="D5" t="n">
-        <v>80.20878743696441</v>
+        <v>80.99418560036187</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.53970886209105</v>
+        <v>35.42145716922493</v>
       </c>
       <c r="C6" t="n">
-        <v>105.1775767990735</v>
+        <v>127.275735873965</v>
       </c>
       <c r="D6" t="n">
-        <v>37.79630486579796</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.59532432386784</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>100.9089377810084</v>
+        <v>124.8036951546715</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>79.94371555681776</v>
+        <v>98.13550051651117</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>47.8140584399324</v>
+        <v>52.91718300660731</v>
       </c>
       <c r="D9" t="n">
         <v>28.6218725696115</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.265112937875643</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="C2" t="n">
-        <v>7.943320675060943</v>
+        <v>7.929576207201487</v>
       </c>
       <c r="D2" t="n">
-        <v>20.58626761035137</v>
+        <v>13.16229147083699</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.72745935331366</v>
+        <v>22.0991408225957</v>
       </c>
       <c r="C3" t="n">
-        <v>22.17277190041422</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="D3" t="n">
-        <v>91.19454424748622</v>
+        <v>66.32687489891451</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.99684343937156</v>
+        <v>44.49084246105696</v>
       </c>
       <c r="C4" t="n">
-        <v>104.411813589761</v>
+        <v>78.27376271189394</v>
       </c>
       <c r="D4" t="n">
-        <v>144.0911105523044</v>
+        <v>124.1557416698686</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.10563750809372</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="C5" t="n">
-        <v>166.4307795624406</v>
+        <v>155.3615741970578</v>
       </c>
       <c r="D5" t="n">
-        <v>105.3660723582889</v>
+        <v>101.4636252339079</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.81896717845365</v>
+        <v>42.66675522656639</v>
       </c>
       <c r="C6" t="n">
-        <v>142.4908617943821</v>
+        <v>168.6141864566855</v>
       </c>
       <c r="D6" t="n">
-        <v>51.6831261423691</v>
+        <v>53.29319237733387</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.31502750653876</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="C7" t="n">
-        <v>126.360747013607</v>
+        <v>154.3876804744449</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.68971097219578</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>105.6458704539993</v>
+        <v>130.179745583127</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>82.98124295375739</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.146501392111027</v>
+        <v>3.401755795215198</v>
       </c>
       <c r="C2" t="n">
-        <v>3.657010198319369</v>
+        <v>3.629521262600458</v>
       </c>
       <c r="D2" t="n">
-        <v>14.18723607407066</v>
+        <v>9.073312282649022</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.75691178444107</v>
+        <v>23.007257449024</v>
       </c>
       <c r="C3" t="n">
-        <v>27.49384445743193</v>
+        <v>23.62084976417826</v>
       </c>
       <c r="D3" t="n">
-        <v>90.31588005218532</v>
+        <v>64.67263001725864</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.85943981850601</v>
+        <v>49.36620156034661</v>
       </c>
       <c r="C4" t="n">
-        <v>97.54547014625882</v>
+        <v>71.82858903351364</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4536785548077</v>
+        <v>130.97103423275</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.63363784652926</v>
+        <v>47.00117134081605</v>
       </c>
       <c r="C5" t="n">
-        <v>196.8404147014855</v>
+        <v>175.9537322936346</v>
       </c>
       <c r="D5" t="n">
-        <v>111.5019955098315</v>
+        <v>110.0539176460675</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.73467574460867</v>
+        <v>34.97868895460962</v>
       </c>
       <c r="C6" t="n">
-        <v>175.0141997406704</v>
+        <v>207.2557760958399</v>
       </c>
       <c r="D6" t="n">
-        <v>50.75733805726436</v>
+        <v>52.04539104523617</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0191362324662</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>134.6849857979157</v>
+        <v>166.6045489060922</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>85.11752595819846</v>
+        <v>101.9741340401162</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.902447124381071</v>
+        <v>3.664864179953343</v>
       </c>
       <c r="C2" t="n">
-        <v>5.726534358871645</v>
+        <v>4.262748531839651</v>
       </c>
       <c r="D2" t="n">
-        <v>12.51630148144259</v>
+        <v>15.62451471308799</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.79279448114169</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="C3" t="n">
-        <v>20.65597169735289</v>
+        <v>18.51085296357361</v>
       </c>
       <c r="D3" t="n">
-        <v>81.60777791551612</v>
+        <v>57.69731257858505</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.88572602234242</v>
+        <v>46.87747113008095</v>
       </c>
       <c r="C4" t="n">
-        <v>83.94041046080653</v>
+        <v>65.91944960165209</v>
       </c>
       <c r="D4" t="n">
-        <v>165.2899887301057</v>
+        <v>133.051357618049</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.80101798233672</v>
+        <v>59.00303702523332</v>
       </c>
       <c r="C5" t="n">
-        <v>190.4590546238812</v>
+        <v>156.5396714421539</v>
       </c>
       <c r="D5" t="n">
-        <v>138.5491447618311</v>
+        <v>128.4862307933013</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.00513938936205</v>
+        <v>46.77242412572655</v>
       </c>
       <c r="C6" t="n">
-        <v>237.5250213131776</v>
+        <v>242.4357233298201</v>
       </c>
       <c r="D6" t="n">
-        <v>67.82404014789091</v>
+        <v>70.35989446796042</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>19.46314823669301</v>
       </c>
       <c r="C7" t="n">
-        <v>187.7445222216388</v>
+        <v>228.1080973340421</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>40.3036885024443</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>123.9211039685536</v>
+        <v>152.3770611761474</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>60.01718240372024</v>
+        <v>69.44686910301085</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.846086594611503</v>
+        <v>2.610467145592269</v>
       </c>
       <c r="C2" t="n">
-        <v>4.25685804561417</v>
+        <v>2.333614292994668</v>
       </c>
       <c r="D2" t="n">
-        <v>10.59600297193582</v>
+        <v>11.34409472257189</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.47725255745097</v>
+        <v>15.54597489674824</v>
       </c>
       <c r="C3" t="n">
-        <v>21.6082669704723</v>
+        <v>17.97089172623786</v>
       </c>
       <c r="D3" t="n">
-        <v>74.88280614142546</v>
+        <v>57.00518044709104</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.56367171762047</v>
+        <v>42.74234979979339</v>
       </c>
       <c r="C4" t="n">
-        <v>72.12213159708342</v>
+        <v>58.4660210310103</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1488380448725</v>
+        <v>132.5536115319958</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.71604790042376</v>
+        <v>64.54991155422779</v>
       </c>
       <c r="C5" t="n">
-        <v>183.218665305061</v>
+        <v>148.1457285708437</v>
       </c>
       <c r="D5" t="n">
-        <v>157.6441376094316</v>
+        <v>141.7152811080271</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.86050368166828</v>
+        <v>56.11080828852221</v>
       </c>
       <c r="C6" t="n">
-        <v>270.5313791299554</v>
+        <v>257.1275777238737</v>
       </c>
       <c r="D6" t="n">
-        <v>82.07312632732911</v>
+        <v>82.99891441243386</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
-        <v>241.1034916951572</v>
+        <v>277.3947773303448</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>45.33416373900496</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>158.135011461555</v>
+        <v>195.3530669295516</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>69.89061906533041</v>
+        <v>82.42655550085793</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.976078202199582</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C2" t="n">
-        <v>13.38809344281375</v>
+        <v>4.680973053848792</v>
       </c>
       <c r="D2" t="n">
-        <v>13.07589767286327</v>
+        <v>14.13422169804133</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.64981916922015</v>
+        <v>12.311116211255</v>
       </c>
       <c r="C3" t="n">
-        <v>19.27661617288612</v>
+        <v>13.77882902910398</v>
       </c>
       <c r="D3" t="n">
-        <v>67.46079349731957</v>
+        <v>53.77523050011904</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.27165068110266</v>
+        <v>36.41204060280995</v>
       </c>
       <c r="C4" t="n">
-        <v>63.87741437681872</v>
+        <v>51.61244030766331</v>
       </c>
       <c r="D4" t="n">
-        <v>166.8598033091964</v>
+        <v>129.503321414901</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.88156235181397</v>
+        <v>65.06532909895736</v>
       </c>
       <c r="C5" t="n">
-        <v>161.448409963388</v>
+        <v>129.9588523496716</v>
       </c>
       <c r="D5" t="n">
-        <v>175.1192467450248</v>
+        <v>153.6926030998382</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.29197394991814</v>
+        <v>68.10580173900973</v>
       </c>
       <c r="C6" t="n">
-        <v>279.7490083251287</v>
+        <v>251.6533525249934</v>
       </c>
       <c r="D6" t="n">
-        <v>102.2392059202628</v>
+        <v>101.9976959850181</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.26754376383641</v>
+        <v>34.85400699617026</v>
       </c>
       <c r="C7" t="n">
-        <v>301.1098748741307</v>
+        <v>317.4589193929529</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>54.79624811253571</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>222.3069501496477</v>
+        <v>266.4512356711056</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>115.1531152219253</v>
+        <v>141.4453004893592</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>56.65666001208344</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.67690719431156</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.658613840829368</v>
+        <v>4.948990177108171</v>
       </c>
       <c r="C2" t="n">
-        <v>7.529023143868788</v>
+        <v>8.615817852470007</v>
       </c>
       <c r="D2" t="n">
-        <v>6.847690237121502</v>
+        <v>12.94041648967721</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.84706834231575</v>
+        <v>3.129811681138832</v>
       </c>
       <c r="C2" t="n">
-        <v>7.603635969391546</v>
+        <v>2.621266370338984</v>
       </c>
       <c r="D2" t="n">
-        <v>9.624072744731482</v>
+        <v>10.4025986741992</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92042168269378</v>
+        <v>16.90569546713007</v>
       </c>
       <c r="C3" t="n">
-        <v>32.00006641992479</v>
+        <v>17.25421590213769</v>
       </c>
       <c r="D3" t="n">
-        <v>73.25801369089699</v>
+        <v>59.49391087735671</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.62971085571225</v>
+        <v>49.86394764639974</v>
       </c>
       <c r="C4" t="n">
-        <v>92.40209392370978</v>
+        <v>73.78128521726053</v>
       </c>
       <c r="D4" t="n">
-        <v>170.816246557311</v>
+        <v>134.0340870700001</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.58330667170541</v>
+        <v>40.76707341884881</v>
       </c>
       <c r="C5" t="n">
-        <v>239.1046533693107</v>
+        <v>204.8662021837032</v>
       </c>
       <c r="D5" t="n">
-        <v>156.6133025199724</v>
+        <v>142.5988540418492</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.74847696573035</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="C6" t="n">
-        <v>253.1426637923358</v>
+        <v>260.8709817201668</v>
       </c>
       <c r="D6" t="n">
-        <v>81.30834486572085</v>
+        <v>80.9863316187279</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.246279805045708</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>156.3040519931347</v>
+        <v>187.3852025618845</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>84.86718029361552</v>
+        <v>104.2272450213626</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>43.26562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.626036240139976</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.737153657169113</v>
+        <v>6.124142179091603</v>
       </c>
       <c r="C2" t="n">
-        <v>4.317726403277472</v>
+        <v>6.920339567235766</v>
       </c>
       <c r="D2" t="n">
-        <v>15.70010928631499</v>
+        <v>14.25792190877643</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26265072084841</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C3" t="n">
-        <v>18.97227438456961</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>8.889725461954868</v>
+        <v>14.00463100108075</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39821907483251</v>
+        <v>13.39745209844084</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14361750941728</v>
+        <v>70.13960216242556</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576261067627355</v>
+        <v>1.576170835110686</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.633268326968198</v>
+        <v>3.806235849364884</v>
       </c>
       <c r="C2" t="n">
-        <v>2.724349879284899</v>
+        <v>3.919136835353267</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6349130272072</v>
+        <v>21.15273603570178</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.57037972063417</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="C3" t="n">
-        <v>17.63709750679395</v>
+        <v>25.01002276568749</v>
       </c>
       <c r="D3" t="n">
-        <v>19.92947839621025</v>
+        <v>22.59492341324034</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.79948678862217</v>
+        <v>12.31602494977624</v>
       </c>
       <c r="C4" t="n">
-        <v>29.46912083837651</v>
+        <v>33.6425303291297</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73116535995239</v>
+        <v>22.41133659254619</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
         <v>5.375068680751288</v>
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44078246174064</v>
+        <v>15.43962601938435</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14331268128988</v>
+        <v>86.13686095024953</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250691044576977</v>
+        <v>3.250447583028284</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.975497365122835</v>
+        <v>6.112361206640642</v>
       </c>
       <c r="C2" t="n">
-        <v>4.971570374305847</v>
+        <v>6.020076922441441</v>
       </c>
       <c r="D2" t="n">
-        <v>23.24778563656447</v>
+        <v>18.34886459237289</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.84741249968102</v>
+        <v>14.79493790299943</v>
       </c>
       <c r="C3" t="n">
-        <v>13.37140373184156</v>
+        <v>19.09008410907923</v>
       </c>
       <c r="D3" t="n">
-        <v>27.01278808235099</v>
+        <v>34.27281235525615</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.82571623919635</v>
+        <v>23.87904941039517</v>
       </c>
       <c r="C4" t="n">
-        <v>38.1350078237631</v>
+        <v>50.70628717664351</v>
       </c>
       <c r="D4" t="n">
-        <v>25.28294862746811</v>
+        <v>28.70335762906399</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.29701189049706</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="C5" t="n">
-        <v>33.33033455917922</v>
+        <v>37.7236555356837</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>30.704159450319</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73507964524098</v>
+        <v>16.73181169199795</v>
       </c>
       <c r="C21" t="n">
-        <v>102.08398583597</v>
+        <v>102.0640513211875</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020523893572292</v>
+        <v>4.182952922999487</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.915029918087032</v>
+        <v>6.356816384998097</v>
       </c>
       <c r="C2" t="n">
-        <v>5.823727381592079</v>
+        <v>5.545892781290231</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6217904541535</v>
+        <v>26.9165768073348</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>18.16724126708723</v>
       </c>
       <c r="C3" t="n">
-        <v>16.78297700409922</v>
+        <v>21.54445336969626</v>
       </c>
       <c r="D3" t="n">
-        <v>38.67104207028186</v>
+        <v>40.59526757060561</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.07570205088079</v>
+        <v>26.58474608329938</v>
       </c>
       <c r="C4" t="n">
-        <v>35.16129402759952</v>
+        <v>49.07265899677682</v>
       </c>
       <c r="D4" t="n">
-        <v>32.71085175779947</v>
+        <v>38.83695743229957</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.61856747360028</v>
+        <v>23.29196428325558</v>
       </c>
       <c r="C5" t="n">
-        <v>53.75068680751288</v>
+        <v>67.56878574478674</v>
       </c>
       <c r="D5" t="n">
-        <v>31.83316931020283</v>
+        <v>33.69848994827177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.00757624419349</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="C6" t="n">
-        <v>33.61013265488955</v>
+        <v>37.35353665118265</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.22921454564179</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.062175209929</v>
+        <v>18.05684283800065</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8341906552511</v>
+        <v>117.7994032764804</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880828651401524</v>
+        <v>6.018947612666882</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.589490590904591</v>
+        <v>6.59930806794706</v>
       </c>
       <c r="C2" t="n">
-        <v>6.8791061636574</v>
+        <v>8.442048508818322</v>
       </c>
       <c r="D2" t="n">
-        <v>32.24255810287374</v>
+        <v>25.15041268739479</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>17.98070920328033</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90846078379357</v>
+        <v>20.238728923048</v>
       </c>
       <c r="D3" t="n">
-        <v>41.60646770597982</v>
+        <v>48.9401230567035</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.49540704221292</v>
+        <v>22.71764187627119</v>
       </c>
       <c r="C4" t="n">
-        <v>32.35349559345364</v>
+        <v>43.32943492693298</v>
       </c>
       <c r="D4" t="n">
-        <v>38.19882142453914</v>
+        <v>43.45706212848506</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.12078032981814</v>
+        <v>19.53677931451153</v>
       </c>
       <c r="C5" t="n">
-        <v>44.54680208019903</v>
+        <v>58.95394964002097</v>
       </c>
       <c r="D5" t="n">
-        <v>29.59969328304134</v>
+        <v>31.93134408062751</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.1006623496477</v>
+        <v>11.43147026824986</v>
       </c>
       <c r="C6" t="n">
-        <v>40.93593402397926</v>
+        <v>50.07305990740432</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>31.396291581813</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>22.69702517448201</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061017301596868</v>
+        <v>7.056782766308251</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19703720247064</v>
+        <v>66.15733843413985</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295762976197651</v>
+        <v>4.410489228942657</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.824128292219578</v>
+        <v>5.862015542057704</v>
       </c>
       <c r="C2" t="n">
-        <v>5.354451978962104</v>
+        <v>6.986116663420303</v>
       </c>
       <c r="D2" t="n">
-        <v>28.0848565753885</v>
+        <v>22.99547647657304</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.04867077905162</v>
+        <v>21.18611545764617</v>
       </c>
       <c r="C3" t="n">
-        <v>24.14117604742907</v>
+        <v>28.46086594611503</v>
       </c>
       <c r="D3" t="n">
-        <v>59.52827204700535</v>
+        <v>58.24218255444202</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.58773238414112</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="C4" t="n">
-        <v>42.00211203079129</v>
+        <v>48.03887866420492</v>
       </c>
       <c r="D4" t="n">
-        <v>51.81664383014665</v>
+        <v>58.6064109527176</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.09748042682348</v>
+        <v>28.00435326364027</v>
       </c>
       <c r="C5" t="n">
-        <v>54.11884219660543</v>
+        <v>71.42214548395546</v>
       </c>
       <c r="D5" t="n">
-        <v>37.52730599483434</v>
+        <v>41.35612204139689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.2566624236317</v>
+        <v>20.28683456055609</v>
       </c>
       <c r="C6" t="n">
-        <v>58.92842419971056</v>
+        <v>76.27688788145595</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>44.37597797966008</v>
+        <v>52.70021676396878</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>25.53525778745954</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286180972954968</v>
+        <v>7.279300433197775</v>
       </c>
       <c r="C21" t="n">
-        <v>76.50490021602717</v>
+        <v>75.52274199442692</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375408351335597</v>
+        <v>5.459475324898331</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.577308707826131</v>
+        <v>4.683918296961532</v>
       </c>
       <c r="C2" t="n">
-        <v>6.682756622808038</v>
+        <v>7.632106652814704</v>
       </c>
       <c r="D2" t="n">
-        <v>32.00988389696725</v>
+        <v>21.35792130588936</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61455836732528</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="C3" t="n">
-        <v>22.11877577668064</v>
+        <v>27.68528525976005</v>
       </c>
       <c r="D3" t="n">
-        <v>68.18237805994099</v>
+        <v>63.12637738306991</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.30543101367455</v>
+        <v>36.53966780436203</v>
       </c>
       <c r="C4" t="n">
-        <v>53.0801531255123</v>
+        <v>61.73327739074368</v>
       </c>
       <c r="D4" t="n">
-        <v>69.50577396526567</v>
+        <v>74.63638746765952</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.01880174176349</v>
+        <v>38.01817984695774</v>
       </c>
       <c r="C5" t="n">
-        <v>67.81422267084844</v>
+        <v>80.69966128908783</v>
       </c>
       <c r="D5" t="n">
-        <v>48.30198704894308</v>
+        <v>52.69530802544756</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.32586778901449</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>74.26430508774999</v>
+        <v>97.32850390362032</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>40.21140421824511</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>66.83345671430585</v>
+        <v>84.7994397020225</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>44.31118263117978</v>
+        <v>50.48637569089222</v>
       </c>
       <c r="D8" t="n">
         <v>34.29735604786232</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
         <v>32.39374724932775</v>
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.499628073282016</v>
+        <v>7.489438633371114</v>
       </c>
       <c r="C21" t="n">
-        <v>86.24572284274318</v>
+        <v>84.25618462542502</v>
       </c>
       <c r="D21" t="n">
-        <v>7.499628073282016</v>
+        <v>6.553258804199724</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_40_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.844976181371</v>
+        <v>10.84497619180755</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907141629683</v>
+        <v>37.78907145266275</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39863062565321</v>
+        <v>6.12512392679585</v>
       </c>
       <c r="C2" t="n">
-        <v>7.447538084416303</v>
+        <v>11.31366054374024</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64789673154067</v>
+        <v>23.83192552059132</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31450342272425</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C3" t="n">
-        <v>28.75048151886784</v>
+        <v>24.20498964820511</v>
       </c>
       <c r="D3" t="n">
-        <v>65.92435834017333</v>
+        <v>72.78186605433729</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.05843150283185</v>
+        <v>34.02541193378595</v>
       </c>
       <c r="C4" t="n">
-        <v>65.85563600087605</v>
+        <v>79.90739089176064</v>
       </c>
       <c r="D4" t="n">
-        <v>87.10556505929826</v>
+        <v>89.95165165390975</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.36303533305563</v>
+        <v>42.87783098297945</v>
       </c>
       <c r="C5" t="n">
-        <v>98.34657627292425</v>
+        <v>109.4894127161256</v>
       </c>
       <c r="D5" t="n">
-        <v>66.78338758138929</v>
+        <v>64.50082416901546</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.0164373357275</v>
+        <v>41.66046382971341</v>
       </c>
       <c r="C6" t="n">
-        <v>112.4631265122891</v>
+        <v>106.4253781311713</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>43.99505987041232</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>28.92523261022377</v>
       </c>
       <c r="C7" t="n">
-        <v>114.1438785819597</v>
+        <v>108.095330976095</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>82.28027509292518</v>
+        <v>76.52232480751763</v>
       </c>
       <c r="D8" t="n">
         <v>36.04977569994287</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>46.03905859065416</v>
+        <v>42.26718391093791</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.685704860481388</v>
+        <v>7.691416027242035</v>
       </c>
       <c r="C21" t="n">
-        <v>93.18917143333682</v>
+        <v>94.21984633371491</v>
       </c>
       <c r="D21" t="n">
-        <v>7.685704860481388</v>
+        <v>8.652843030647288</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.749335540247575</v>
+        <v>6.607162049581034</v>
       </c>
       <c r="C2" t="n">
-        <v>4.909720268938299</v>
+        <v>11.11927449829937</v>
       </c>
       <c r="D2" t="n">
-        <v>23.24778563656447</v>
+        <v>28.72495607855743</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.11815388187489</v>
+        <v>19.30606860401353</v>
       </c>
       <c r="C3" t="n">
-        <v>28.69157665661304</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D3" t="n">
-        <v>64.52536786162162</v>
+        <v>74.19558274845269</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="C4" t="n">
-        <v>68.11463746834795</v>
+        <v>69.32709588309277</v>
       </c>
       <c r="D4" t="n">
-        <v>97.36679206408591</v>
+        <v>103.4163214176548</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.68901662859458</v>
+        <v>46.4612101034803</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6121311791564</v>
+        <v>127.9708132485718</v>
       </c>
       <c r="D5" t="n">
-        <v>81.19053514121123</v>
+        <v>78.56436003235102</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.87809302488671</v>
+        <v>49.1875234781737</v>
       </c>
       <c r="C6" t="n">
-        <v>132.2669412023558</v>
+        <v>137.3386498424948</v>
       </c>
       <c r="D6" t="n">
-        <v>55.30577517103983</v>
+        <v>52.89067581859268</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.89015173477814</v>
+        <v>38.86640986342697</v>
       </c>
       <c r="C7" t="n">
-        <v>138.0386359556228</v>
+        <v>130.6725829306589</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>22.36421270274234</v>
       </c>
       <c r="C8" t="n">
-        <v>114.491417269263</v>
+        <v>107.6486357706628</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>67.22811929141305</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>28.35778243716912</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.867498853733873</v>
+        <v>7.872266490526308</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2940477418236</v>
+        <v>102.339464376842</v>
       </c>
       <c r="D21" t="n">
-        <v>8.850936210450607</v>
+        <v>9.840333113157884</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.18130453011617</v>
+        <v>8.018915248287946</v>
       </c>
       <c r="C2" t="n">
-        <v>4.719261214314417</v>
+        <v>8.665886985386596</v>
       </c>
       <c r="D2" t="n">
-        <v>22.54092728950677</v>
+        <v>28.69059490890879</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.86490403190821</v>
+        <v>20.238728923048</v>
       </c>
       <c r="C3" t="n">
-        <v>23.90555659840983</v>
+        <v>38.53850613020854</v>
       </c>
       <c r="D3" t="n">
-        <v>66.91101478294136</v>
+        <v>78.92269794440108</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.66354794154638</v>
+        <v>34.68907338185679</v>
       </c>
       <c r="C4" t="n">
-        <v>68.90592611797088</v>
+        <v>75.72121868085225</v>
       </c>
       <c r="D4" t="n">
-        <v>105.2158649595392</v>
+        <v>112.1587847239726</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.47441479199203</v>
+        <v>48.71922982324798</v>
       </c>
       <c r="C5" t="n">
-        <v>116.5579961867026</v>
+        <v>126.3263858439583</v>
       </c>
       <c r="D5" t="n">
-        <v>93.19240082562848</v>
+        <v>92.72607066611126</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.72716592033996</v>
+        <v>54.6214970211798</v>
       </c>
       <c r="C6" t="n">
-        <v>149.3738949488565</v>
+        <v>166.0380804807419</v>
       </c>
       <c r="D6" t="n">
-        <v>65.77120569831082</v>
+        <v>63.11459641061895</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.31042186765379</v>
+        <v>47.01098881785852</v>
       </c>
       <c r="C7" t="n">
-        <v>162.113053159163</v>
+        <v>158.8791762213741</v>
       </c>
       <c r="D7" t="n">
-        <v>48.20872101703962</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.87319998189869</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C8" t="n">
-        <v>143.7818600254666</v>
+        <v>135.6873502039516</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>102.2843663146582</v>
+        <v>96.18280433276422</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>61.06961594267285</v>
+        <v>56.22959976073607</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>38.38240824523329</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.033940095816908</v>
+        <v>8.036740026823505</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4624338055053</v>
+        <v>110.5051753688232</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04242511977113</v>
+        <v>11.05051753688232</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.328165775125692</v>
+        <v>7.319910882864218</v>
       </c>
       <c r="C2" t="n">
-        <v>3.171045084717197</v>
+        <v>5.892449720889356</v>
       </c>
       <c r="D2" t="n">
-        <v>18.54619588092649</v>
+        <v>23.70920705756047</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.96722677732814</v>
+        <v>24.12644983186537</v>
       </c>
       <c r="C3" t="n">
-        <v>36.65355053805467</v>
+        <v>54.2170169670301</v>
       </c>
       <c r="D3" t="n">
-        <v>73.70470889632928</v>
+        <v>85.22551820566561</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.20637230653686</v>
+        <v>23.40682876465245</v>
       </c>
       <c r="C4" t="n">
-        <v>96.54997797415255</v>
+        <v>104.4883899106923</v>
       </c>
       <c r="D4" t="n">
-        <v>102.7143718091183</v>
+        <v>106.5431878556809</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.08489763311751</v>
+        <v>30.75324683553134</v>
       </c>
       <c r="C5" t="n">
-        <v>89.24086631603508</v>
+        <v>99.20560551414022</v>
       </c>
       <c r="D5" t="n">
-        <v>65.23713494720056</v>
+        <v>62.63550353094652</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.34345713223292</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C6" t="n">
-        <v>106.7473913781642</v>
+        <v>104.6140536168359</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>101.0885976108856</v>
+        <v>95.39936966477529</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>75.35404503946393</v>
+        <v>70.84782307697107</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.792892292132928</v>
+        <v>4.538619636733004</v>
       </c>
       <c r="C2" t="n">
-        <v>2.216786316189298</v>
+        <v>2.911863690796039</v>
       </c>
       <c r="D2" t="n">
-        <v>13.35471402086936</v>
+        <v>16.60331717422206</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.0387144332889</v>
+        <v>25.27509464583413</v>
       </c>
       <c r="C3" t="n">
-        <v>24.53878386764903</v>
+        <v>39.08337610606552</v>
       </c>
       <c r="D3" t="n">
-        <v>72.04555527615217</v>
+        <v>84.8475453395306</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.01639627799848</v>
+        <v>33.11925880276615</v>
       </c>
       <c r="C4" t="n">
-        <v>96.72865605632549</v>
+        <v>122.1264691651905</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2090748410674</v>
+        <v>123.0198595760551</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.01188845010476</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>132.3886779176824</v>
+        <v>143.8751260573701</v>
       </c>
       <c r="D5" t="n">
-        <v>80.99418560036187</v>
+        <v>79.66882619962867</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.42145716922493</v>
+        <v>34.37491411649783</v>
       </c>
       <c r="C6" t="n">
-        <v>127.275735873965</v>
+        <v>130.0128484734051</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>124.8036951546715</v>
+        <v>120.2523127977833</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>98.13550051651117</v>
+        <v>91.70996179221579</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>52.91718300660731</v>
+        <v>48.25780840225195</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
         <v>21.04572553593887</v>
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.836490101747288</v>
+        <v>5.549819772107219</v>
       </c>
       <c r="C2" t="n">
-        <v>7.929576207201487</v>
+        <v>10.31522312852124</v>
       </c>
       <c r="D2" t="n">
-        <v>13.16229147083699</v>
+        <v>17.23948968657399</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.0991408225957</v>
+        <v>20.50870954171587</v>
       </c>
       <c r="C3" t="n">
-        <v>16.00248757922301</v>
+        <v>24.44060909722435</v>
       </c>
       <c r="D3" t="n">
-        <v>66.32687489891451</v>
+        <v>78.89324551327368</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.49084246105696</v>
+        <v>40.16428032844126</v>
       </c>
       <c r="C4" t="n">
-        <v>78.27376271189394</v>
+        <v>109.5424270921549</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1557416698686</v>
+        <v>135.195494604124</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.13585070274711</v>
+        <v>41.42975311921541</v>
       </c>
       <c r="C5" t="n">
-        <v>155.3615741970578</v>
+        <v>183.6604517719721</v>
       </c>
       <c r="D5" t="n">
-        <v>101.4636252339079</v>
+        <v>101.340906770877</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>168.6141864566855</v>
+        <v>177.7915639959847</v>
       </c>
       <c r="D6" t="n">
-        <v>53.29319237733387</v>
+        <v>50.51582812201963</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3876804744449</v>
+        <v>152.8905152254685</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>13.4352173326176</v>
       </c>
       <c r="C8" t="n">
-        <v>130.179745583127</v>
+        <v>123.0031698650829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>82.98124295375739</v>
+        <v>76.10311853780424</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.401755795215198</v>
+        <v>3.266274612029138</v>
       </c>
       <c r="C2" t="n">
-        <v>3.629521262600458</v>
+        <v>4.822344723260333</v>
       </c>
       <c r="D2" t="n">
-        <v>9.073312282649022</v>
+        <v>12.03524510636165</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.007257449024</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="C3" t="n">
-        <v>23.62084976417826</v>
+        <v>32.81491701444963</v>
       </c>
       <c r="D3" t="n">
-        <v>64.67263001725864</v>
+        <v>77.88204537789947</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.36620156034661</v>
+        <v>44.09519813624549</v>
       </c>
       <c r="C4" t="n">
-        <v>71.82858903351364</v>
+        <v>102.7654226897391</v>
       </c>
       <c r="D4" t="n">
-        <v>130.97103423275</v>
+        <v>144.1166359926148</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.00117134081605</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>175.9537322936346</v>
+        <v>218.3406894244907</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0539176460675</v>
+        <v>107.108674533327</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>33.48937768726721</v>
       </c>
       <c r="C6" t="n">
-        <v>207.2557760958399</v>
+        <v>211.4419483067483</v>
       </c>
       <c r="D6" t="n">
-        <v>52.04539104523617</v>
+        <v>49.67054334866313</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.384125394267761</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>166.6045489060922</v>
+        <v>160.0769084205552</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>101.9741340401162</v>
+        <v>93.46238144429634</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.664864179953343</v>
+        <v>3.486186097780424</v>
       </c>
       <c r="C2" t="n">
-        <v>4.262748531839651</v>
+        <v>8.379216655746527</v>
       </c>
       <c r="D2" t="n">
-        <v>15.62451471308799</v>
+        <v>12.23846688114074</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47510913559323</v>
+        <v>16.60135367881356</v>
       </c>
       <c r="C3" t="n">
-        <v>18.51085296357361</v>
+        <v>25.70706363570273</v>
       </c>
       <c r="D3" t="n">
-        <v>57.69731257858505</v>
+        <v>70.98526775556563</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.87747113008095</v>
+        <v>43.11246868429443</v>
       </c>
       <c r="C4" t="n">
-        <v>65.91944960165209</v>
+        <v>93.39758609581605</v>
       </c>
       <c r="D4" t="n">
-        <v>133.051357618049</v>
+        <v>148.6984525283346</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.00303702523332</v>
+        <v>52.89165756629692</v>
       </c>
       <c r="C5" t="n">
-        <v>156.5396714421539</v>
+        <v>206.7315228217722</v>
       </c>
       <c r="D5" t="n">
-        <v>128.4862307933013</v>
+        <v>128.3144249450581</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.77242412572655</v>
+        <v>42.9082651618111</v>
       </c>
       <c r="C6" t="n">
-        <v>242.4357233298201</v>
+        <v>272.1414453649201</v>
       </c>
       <c r="D6" t="n">
-        <v>70.35989446796042</v>
+        <v>65.9322123218073</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>228.1080973340421</v>
+        <v>222.1194363381366</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>152.3770611761474</v>
+        <v>143.1142715865788</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>69.44686910301085</v>
+        <v>62.12499472473814</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3173,7 +3173,7 @@
         <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.610467145592269</v>
+        <v>2.418044595559894</v>
       </c>
       <c r="C2" t="n">
-        <v>2.333614292994668</v>
+        <v>4.625013434706723</v>
       </c>
       <c r="D2" t="n">
-        <v>11.34409472257189</v>
+        <v>9.108655200001905</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.54597489674824</v>
+        <v>14.78021168743573</v>
       </c>
       <c r="C3" t="n">
-        <v>17.97089172623786</v>
+        <v>29.05973204570559</v>
       </c>
       <c r="D3" t="n">
-        <v>57.00518044709104</v>
+        <v>66.62630794870978</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.74234979979339</v>
+        <v>39.67929696254333</v>
       </c>
       <c r="C4" t="n">
-        <v>58.4660210310103</v>
+        <v>83.4299016545982</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5536115319958</v>
+        <v>150.0768263050971</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.54991155422779</v>
+        <v>58.53670686571608</v>
       </c>
       <c r="C5" t="n">
-        <v>148.1457285708437</v>
+        <v>200.7183181332604</v>
       </c>
       <c r="D5" t="n">
-        <v>141.7152811080271</v>
+        <v>142.279786037969</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.11080828852221</v>
+        <v>50.19381487502668</v>
       </c>
       <c r="C6" t="n">
-        <v>257.1275777238737</v>
+        <v>303.5779886026073</v>
       </c>
       <c r="D6" t="n">
-        <v>82.99891441243386</v>
+        <v>79.5372720072596</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>277.3947773303448</v>
+        <v>280.2094479984203</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>195.3530669295516</v>
+        <v>182.4185409260998</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>82.42655550085793</v>
+        <v>70.55624400880974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3470,7 +3470,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.422773407631881</v>
+        <v>3.168099841604457</v>
       </c>
       <c r="C2" t="n">
-        <v>4.680973053848792</v>
+        <v>10.45168605941154</v>
       </c>
       <c r="D2" t="n">
-        <v>14.13422169804133</v>
+        <v>15.49197877301467</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.311116211255</v>
+        <v>11.66316272645211</v>
       </c>
       <c r="C3" t="n">
-        <v>13.77882902910398</v>
+        <v>24.03809253848316</v>
       </c>
       <c r="D3" t="n">
-        <v>53.77523050011904</v>
+        <v>59.82770509680063</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.41204060280995</v>
+        <v>34.10198825471721</v>
       </c>
       <c r="C4" t="n">
-        <v>51.61244030766331</v>
+        <v>77.63562670413351</v>
       </c>
       <c r="D4" t="n">
-        <v>129.503321414901</v>
+        <v>148.8388424500419</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.06532909895736</v>
+        <v>58.75760009917161</v>
       </c>
       <c r="C5" t="n">
-        <v>129.9588523496716</v>
+        <v>180.2979658849268</v>
       </c>
       <c r="D5" t="n">
-        <v>153.6926030998382</v>
+        <v>157.6195939168254</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.10580173900973</v>
+        <v>60.86050368166828</v>
       </c>
       <c r="C6" t="n">
-        <v>251.6533525249934</v>
+        <v>313.8019091946335</v>
       </c>
       <c r="D6" t="n">
-        <v>101.9976959850181</v>
+        <v>97.69076880648737</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.85400699617026</v>
+        <v>31.08115056874977</v>
       </c>
       <c r="C7" t="n">
-        <v>317.4589193929529</v>
+        <v>342.2519759160018</v>
       </c>
       <c r="D7" t="n">
-        <v>54.79624811253571</v>
+        <v>51.92169083450106</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>266.4512356711056</v>
+        <v>253.6836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>141.4453004893592</v>
+        <v>126.8015517328137</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>56.65666001208344</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3739,7 +3739,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.948990177108171</v>
+        <v>4.769330347231005</v>
       </c>
       <c r="C2" t="n">
-        <v>8.615817852470007</v>
+        <v>7.007715112913733</v>
       </c>
       <c r="D2" t="n">
-        <v>12.94041648967721</v>
+        <v>7.580074024489623</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.129811681138832</v>
+        <v>2.292380889416302</v>
       </c>
       <c r="C2" t="n">
-        <v>2.621266370338984</v>
+        <v>6.020076922441441</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4025986741992</v>
+        <v>11.52571804785755</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90569546713007</v>
+        <v>15.44780012632356</v>
       </c>
       <c r="C3" t="n">
-        <v>17.25421590213769</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="D3" t="n">
-        <v>59.49391087735671</v>
+        <v>65.61510781333557</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.86394764639974</v>
+        <v>45.67777543549135</v>
       </c>
       <c r="C4" t="n">
-        <v>73.78128521726053</v>
+        <v>110.2316139805361</v>
       </c>
       <c r="D4" t="n">
-        <v>134.0340870700001</v>
+        <v>152.5527940152076</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.76707341884881</v>
+        <v>35.36746104549135</v>
       </c>
       <c r="C5" t="n">
-        <v>204.8662021837032</v>
+        <v>267.8453174111361</v>
       </c>
       <c r="D5" t="n">
-        <v>142.5988540418492</v>
+        <v>142.6724851196678</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.61513920440203</v>
+        <v>19.28054316370311</v>
       </c>
       <c r="C6" t="n">
-        <v>260.8709817201668</v>
+        <v>283.8546772242889</v>
       </c>
       <c r="D6" t="n">
-        <v>80.9863316187279</v>
+        <v>77.60519252530189</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>187.3852025618845</v>
+        <v>178.4022110680261</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>104.2272450213626</v>
+        <v>93.46238144429634</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>43.26562132615692</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4347,7 +4347,7 @@
         <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.124142179091603</v>
+        <v>6.952737241475911</v>
       </c>
       <c r="C2" t="n">
-        <v>6.920339567235766</v>
+        <v>7.252170291271189</v>
       </c>
       <c r="D2" t="n">
-        <v>14.25792190877643</v>
+        <v>11.1722888743287</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.51451791248334</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71135047941821</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D3" t="n">
-        <v>14.00463100108075</v>
+        <v>9.503317777109125</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39745209844084</v>
+        <v>13.39867932596747</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13960216242556</v>
+        <v>70.14602705947675</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576170835110686</v>
+        <v>1.576315214819702</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.806235849364884</v>
+        <v>5.561600744558181</v>
       </c>
       <c r="C2" t="n">
-        <v>3.919136835353267</v>
+        <v>4.696681017116741</v>
       </c>
       <c r="D2" t="n">
-        <v>21.15273603570178</v>
+        <v>20.30548776693678</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8811517745239</v>
+        <v>18.41267819314893</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01002276568749</v>
+        <v>24.5927799913826</v>
       </c>
       <c r="D3" t="n">
-        <v>22.59492341324034</v>
+        <v>16.5915362017711</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.31602494977624</v>
+        <v>11.86932974434394</v>
       </c>
       <c r="C4" t="n">
-        <v>33.6425303291297</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="D4" t="n">
-        <v>22.41133659254619</v>
+        <v>20.05023336383261</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43962601938435</v>
+        <v>15.44305641684494</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13686095024953</v>
+        <v>86.15599895713497</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250447583028284</v>
+        <v>3.251169771967357</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.112361206640642</v>
+        <v>4.984333094461056</v>
       </c>
       <c r="C2" t="n">
-        <v>6.020076922441441</v>
+        <v>4.130212591766331</v>
       </c>
       <c r="D2" t="n">
-        <v>18.34886459237289</v>
+        <v>27.18753917370692</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.79493790299943</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C3" t="n">
-        <v>19.09008410907923</v>
+        <v>20.75905520629881</v>
       </c>
       <c r="D3" t="n">
-        <v>34.27281235525615</v>
+        <v>28.98610096788708</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.87904941039517</v>
+        <v>25.23189774684727</v>
       </c>
       <c r="C4" t="n">
-        <v>50.70628717664351</v>
+        <v>47.54113257815179</v>
       </c>
       <c r="D4" t="n">
-        <v>28.70335762906399</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.99557428756428</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="C5" t="n">
-        <v>37.7236555356837</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="D5" t="n">
-        <v>30.704159450319</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73181169199795</v>
+        <v>16.73778456121089</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0640513211875</v>
+        <v>102.1004858233864</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182952922999487</v>
+        <v>5.021335368363267</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.356816384998097</v>
+        <v>4.723188205131405</v>
       </c>
       <c r="C2" t="n">
-        <v>5.545892781290231</v>
+        <v>5.869869523691679</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9165768073348</v>
+        <v>24.38661297349077</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.16724126708723</v>
+        <v>17.90216938694059</v>
       </c>
       <c r="C3" t="n">
-        <v>21.54445336969626</v>
+        <v>18.0199791114502</v>
       </c>
       <c r="D3" t="n">
-        <v>40.59526757060561</v>
+        <v>43.20180772538089</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.58474608329938</v>
+        <v>31.49839334305466</v>
       </c>
       <c r="C4" t="n">
-        <v>49.07265899677682</v>
+        <v>50.00433756810704</v>
       </c>
       <c r="D4" t="n">
-        <v>38.83695743229957</v>
+        <v>32.53217367562655</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.29196428325558</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C5" t="n">
-        <v>67.56878574478674</v>
+        <v>61.45740628585034</v>
       </c>
       <c r="D5" t="n">
-        <v>33.69848994827177</v>
+        <v>31.26866438026092</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.50568218314512</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>37.35353665118265</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05684283800065</v>
+        <v>18.06430989808625</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7994032764804</v>
+        <v>117.8481169541817</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018947612666882</v>
+        <v>6.881641865937619</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.59930806794706</v>
+        <v>5.970989537229101</v>
       </c>
       <c r="C2" t="n">
-        <v>8.442048508818322</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D2" t="n">
-        <v>25.15041268739479</v>
+        <v>28.80349589489717</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98070920328033</v>
+        <v>15.06000978314607</v>
       </c>
       <c r="C3" t="n">
-        <v>20.238728923048</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="D3" t="n">
-        <v>48.9401230567035</v>
+        <v>49.03829782712818</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.71764187627119</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="C4" t="n">
-        <v>43.32943492693298</v>
+        <v>39.15602543617979</v>
       </c>
       <c r="D4" t="n">
-        <v>43.45706212848506</v>
+        <v>40.24085664937251</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.53677931451153</v>
+        <v>21.94206118991621</v>
       </c>
       <c r="C5" t="n">
-        <v>58.95394964002097</v>
+        <v>58.29126993965438</v>
       </c>
       <c r="D5" t="n">
-        <v>31.93134408062751</v>
+        <v>28.69157665661304</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.43147026824986</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>50.07305990740432</v>
+        <v>44.84034464376883</v>
       </c>
       <c r="D6" t="n">
-        <v>31.396291581813</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056782766308251</v>
+        <v>7.060906399463991</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15733843413985</v>
+        <v>66.19599749497492</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410489228942657</v>
+        <v>5.295679799597993</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.862015542057704</v>
+        <v>5.324999547834699</v>
       </c>
       <c r="C2" t="n">
-        <v>6.986116663420303</v>
+        <v>7.777405313043232</v>
       </c>
       <c r="D2" t="n">
-        <v>22.99547647657304</v>
+        <v>25.01885849502571</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.18611545764617</v>
+        <v>18.68756755033803</v>
       </c>
       <c r="C3" t="n">
-        <v>28.46086594611503</v>
+        <v>38.39615271309275</v>
       </c>
       <c r="D3" t="n">
-        <v>58.24218255444202</v>
+        <v>62.06608986248335</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.59224021203486</v>
+        <v>27.72062817711294</v>
       </c>
       <c r="C4" t="n">
-        <v>48.03887866420492</v>
+        <v>45.43528375254238</v>
       </c>
       <c r="D4" t="n">
-        <v>58.6064109527176</v>
+        <v>57.44500341859361</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.00435326364027</v>
+        <v>30.23782929080177</v>
       </c>
       <c r="C5" t="n">
-        <v>71.42214548395546</v>
+        <v>67.20063035569419</v>
       </c>
       <c r="D5" t="n">
-        <v>41.35612204139689</v>
+        <v>37.62548076525901</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.28683456055609</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>76.27688788145595</v>
+        <v>73.49952362614172</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>33.08686112852601</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>52.70021676396878</v>
+        <v>47.19064864773568</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>26.78698611037422</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279300433197775</v>
+        <v>7.284392154917953</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52274199442692</v>
+        <v>75.57556860727377</v>
       </c>
       <c r="D21" t="n">
-        <v>5.459475324898331</v>
+        <v>6.373843135553209</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.683918296961532</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C2" t="n">
-        <v>7.632106652814704</v>
+        <v>4.432590884674349</v>
       </c>
       <c r="D2" t="n">
-        <v>21.35792130588936</v>
+        <v>25.66583023212436</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.69524160552276</v>
+        <v>18.55503161026472</v>
       </c>
       <c r="C3" t="n">
-        <v>27.68528525976005</v>
+        <v>33.46287049925253</v>
       </c>
       <c r="D3" t="n">
-        <v>63.12637738306991</v>
+        <v>67.68168673077511</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.53966780436203</v>
+        <v>32.55769911593697</v>
       </c>
       <c r="C4" t="n">
-        <v>61.73327739074368</v>
+        <v>75.28728619557515</v>
       </c>
       <c r="D4" t="n">
-        <v>74.63638746765952</v>
+        <v>75.64464235992098</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.01817984695774</v>
+        <v>36.86462629446773</v>
       </c>
       <c r="C5" t="n">
-        <v>80.69966128908783</v>
+        <v>76.18362184955249</v>
       </c>
       <c r="D5" t="n">
-        <v>52.69530802544756</v>
+        <v>49.40645321622075</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="C6" t="n">
-        <v>97.32850390362032</v>
+        <v>92.37755023110364</v>
       </c>
       <c r="D6" t="n">
-        <v>40.21140421824511</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>84.7994397020225</v>
+        <v>80.00851090529807</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>50.48637569089222</v>
+        <v>45.64635950895544</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489438633371114</v>
+        <v>7.495105339830831</v>
       </c>
       <c r="C21" t="n">
-        <v>84.25618462542502</v>
+        <v>85.2568232405757</v>
       </c>
       <c r="D21" t="n">
-        <v>6.553258804199724</v>
+        <v>7.495105339830831</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_40_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619180755</v>
+        <v>10.84497647301474</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907145266275</v>
+        <v>37.78907243252277</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.12512392679585</v>
+        <v>1.254673566027424</v>
       </c>
       <c r="C2" t="n">
-        <v>11.31366054374024</v>
+        <v>1.675843331149305</v>
       </c>
       <c r="D2" t="n">
-        <v>23.83192552059132</v>
+        <v>10.70694046251571</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25068982194821</v>
+        <v>9.704576056479722</v>
       </c>
       <c r="C3" t="n">
-        <v>24.20498964820511</v>
+        <v>22.07950586851076</v>
       </c>
       <c r="D3" t="n">
-        <v>72.78186605433729</v>
+        <v>53.20090809313465</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.02541193378595</v>
+        <v>14.99619618237003</v>
       </c>
       <c r="C4" t="n">
-        <v>79.90739089176064</v>
+        <v>90.28348237794518</v>
       </c>
       <c r="D4" t="n">
-        <v>89.95165165390975</v>
+        <v>71.81582631335841</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.87783098297945</v>
+        <v>14.48077863764046</v>
       </c>
       <c r="C5" t="n">
-        <v>109.4894127161256</v>
+        <v>114.9871998599077</v>
       </c>
       <c r="D5" t="n">
-        <v>64.50082416901546</v>
+        <v>49.5291716792516</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.66046382971341</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="C6" t="n">
-        <v>106.4253781311713</v>
+        <v>74.94858323761002</v>
       </c>
       <c r="D6" t="n">
-        <v>43.99505987041232</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.92523261022377</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>108.095330976095</v>
+        <v>43.77711188006952</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>76.52232480751763</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26718391093791</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691416027242035</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.21984633371491</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.652843030647288</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.607162049581034</v>
+        <v>1.451023106876786</v>
       </c>
       <c r="C2" t="n">
-        <v>11.11927449829937</v>
+        <v>3.61675854244525</v>
       </c>
       <c r="D2" t="n">
-        <v>28.72495607855743</v>
+        <v>20.42820622996763</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30606860401353</v>
+        <v>6.837872760079034</v>
       </c>
       <c r="C3" t="n">
-        <v>34.24335992412875</v>
+        <v>12.85598618711198</v>
       </c>
       <c r="D3" t="n">
-        <v>74.19558274845269</v>
+        <v>49.42117943178444</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.37000537797658</v>
+        <v>17.25519764984194</v>
       </c>
       <c r="C4" t="n">
-        <v>69.32709588309277</v>
+        <v>70.09285909240528</v>
       </c>
       <c r="D4" t="n">
-        <v>103.4163214176548</v>
+        <v>82.3961213220263</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.4612101034803</v>
+        <v>18.70229376590174</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9708132485718</v>
+        <v>145.2004854581033</v>
       </c>
       <c r="D5" t="n">
-        <v>78.56436003235102</v>
+        <v>64.15721247252907</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.1875234781737</v>
+        <v>14.85286101755</v>
       </c>
       <c r="C6" t="n">
-        <v>137.3386498424948</v>
+        <v>132.669457761097</v>
       </c>
       <c r="D6" t="n">
-        <v>52.89067581859268</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.86640986342697</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>130.6725829306589</v>
+        <v>77.37350006709961</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.36421270274234</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>107.6486357706628</v>
+        <v>44.2277340763188</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.872266490526308</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.339464376842</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.840333113157884</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.018915248287946</v>
+        <v>0.7549639845657972</v>
       </c>
       <c r="C2" t="n">
-        <v>8.665886985386596</v>
+        <v>1.466731070144735</v>
       </c>
       <c r="D2" t="n">
-        <v>28.69059490890879</v>
+        <v>13.79159174925919</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.238728923048</v>
+        <v>6.690610604442013</v>
       </c>
       <c r="C3" t="n">
-        <v>38.53850613020854</v>
+        <v>14.38751260573701</v>
       </c>
       <c r="D3" t="n">
-        <v>78.92269794440108</v>
+        <v>54.82079180514189</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.68907338185679</v>
+        <v>18.97816487079509</v>
       </c>
       <c r="C4" t="n">
-        <v>75.72121868085225</v>
+        <v>61.24829402484576</v>
       </c>
       <c r="D4" t="n">
-        <v>112.1587847239726</v>
+        <v>89.14760028413161</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.71922982324798</v>
+        <v>19.02136176978195</v>
       </c>
       <c r="C5" t="n">
-        <v>126.3263858439583</v>
+        <v>158.7976911619216</v>
       </c>
       <c r="D5" t="n">
-        <v>92.72607066611126</v>
+        <v>72.77204857729483</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.6214970211798</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="C6" t="n">
-        <v>166.0380804807419</v>
+        <v>172.9613652910903</v>
       </c>
       <c r="D6" t="n">
-        <v>63.11459641061895</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.01098881785852</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>158.8791762213741</v>
+        <v>75.69667498824607</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.54217107911827</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>135.6873502039516</v>
+        <v>42.30841731451629</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>96.18280433276422</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.38240824523329</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036740026823505</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5051753688232</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05051753688232</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.319910882864218</v>
+        <v>0.8924086631603507</v>
       </c>
       <c r="C2" t="n">
-        <v>5.892449720889356</v>
+        <v>3.781692156758713</v>
       </c>
       <c r="D2" t="n">
-        <v>23.70920705756047</v>
+        <v>13.11124059021615</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.12644983186537</v>
+        <v>4.550400609183966</v>
       </c>
       <c r="C3" t="n">
-        <v>54.2170169670301</v>
+        <v>9.341329405908402</v>
       </c>
       <c r="D3" t="n">
-        <v>85.22551820566561</v>
+        <v>53.10764206123121</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.40682876465245</v>
+        <v>16.04273923509713</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4883899106923</v>
+        <v>47.51560713784138</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5431878556809</v>
+        <v>96.16709636949631</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.75324683553134</v>
+        <v>24.12644983186537</v>
       </c>
       <c r="C5" t="n">
-        <v>99.20560551414022</v>
+        <v>137.2728727463103</v>
       </c>
       <c r="D5" t="n">
-        <v>62.63550353094652</v>
+        <v>88.28366230439444</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.18245050873644</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>104.6140536168359</v>
+        <v>214.8230874001744</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18874190558942</v>
+        <v>50.91834468076083</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>95.39936966477529</v>
+        <v>160.7955477400638</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>70.84782307697107</v>
+        <v>70.09678608322226</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.538619636733004</v>
+        <v>0.5114905539125882</v>
       </c>
       <c r="C2" t="n">
-        <v>2.911863690796039</v>
+        <v>1.999820073550753</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60331717422206</v>
+        <v>9.063494805606554</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.27509464583413</v>
+        <v>3.941717032550944</v>
       </c>
       <c r="C3" t="n">
-        <v>39.08337610606552</v>
+        <v>12.4976482750619</v>
       </c>
       <c r="D3" t="n">
-        <v>84.8475453395306</v>
+        <v>52.26333903557895</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.11925880276615</v>
+        <v>13.42638160327938</v>
       </c>
       <c r="C4" t="n">
-        <v>122.1264691651905</v>
+        <v>36.74387132684537</v>
       </c>
       <c r="D4" t="n">
-        <v>123.0198595760551</v>
+        <v>100.5957602633537</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>25.6727024660541</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8751260573701</v>
+        <v>119.8468509959294</v>
       </c>
       <c r="D5" t="n">
-        <v>79.66882619962867</v>
+        <v>100.2609842962055</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.37491411649783</v>
+        <v>23.0239471599962</v>
       </c>
       <c r="C6" t="n">
-        <v>130.0128484734051</v>
+        <v>227.4218556887737</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>61.18251692866124</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>120.2523127977833</v>
+        <v>223.1375087074405</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>91.70996179221579</v>
+        <v>109.4010554227433</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>48.25780840225195</v>
+        <v>51.47499562906875</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.549819772107219</v>
+        <v>1.034762080276138</v>
       </c>
       <c r="C2" t="n">
-        <v>10.31522312852124</v>
+        <v>13.4185276216454</v>
       </c>
       <c r="D2" t="n">
-        <v>17.23948968657399</v>
+        <v>10.55182432524472</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50870954171587</v>
+        <v>2.812707172667112</v>
       </c>
       <c r="C3" t="n">
-        <v>24.44060909722435</v>
+        <v>9.99419162923253</v>
       </c>
       <c r="D3" t="n">
-        <v>78.89324551327368</v>
+        <v>47.66385104118265</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.16428032844126</v>
+        <v>10.60582044897829</v>
       </c>
       <c r="C4" t="n">
-        <v>109.5424270921549</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D4" t="n">
-        <v>135.195494604124</v>
+        <v>103.6332876602933</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>23.73375075016664</v>
       </c>
       <c r="C5" t="n">
-        <v>183.6604517719721</v>
+        <v>93.73236206296423</v>
       </c>
       <c r="D5" t="n">
-        <v>101.340906770877</v>
+        <v>112.4101121362598</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>177.7915639959847</v>
+        <v>213.1325178534614</v>
       </c>
       <c r="D6" t="n">
-        <v>50.51582812201963</v>
+        <v>76.1963845697077</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>152.8905152254685</v>
+        <v>273.8015807328014</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>123.0031698650829</v>
+        <v>195.3530669295516</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>76.10311853780424</v>
+        <v>88.74999246391164</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
+        <v>32.87382187670443</v>
+      </c>
+      <c r="D11" t="n">
         <v>33.7623035490478</v>
-      </c>
-      <c r="D11" t="n">
-        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.8226478228966</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.266274612029138</v>
+        <v>0.6783876636345459</v>
       </c>
       <c r="C2" t="n">
-        <v>4.822344723260333</v>
+        <v>6.763259934556276</v>
       </c>
       <c r="D2" t="n">
-        <v>12.03524510636165</v>
+        <v>7.597745483166066</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.6377194015997</v>
+        <v>4.216606389740051</v>
       </c>
       <c r="C3" t="n">
-        <v>32.81491701444963</v>
+        <v>27.62638039750524</v>
       </c>
       <c r="D3" t="n">
-        <v>77.88204537789947</v>
+        <v>51.05088062083414</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.09519813624549</v>
+        <v>16.6042989219263</v>
       </c>
       <c r="C4" t="n">
-        <v>102.7654226897391</v>
+        <v>48.91950635491432</v>
       </c>
       <c r="D4" t="n">
-        <v>144.1166359926148</v>
+        <v>109.0319182859465</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C5" t="n">
-        <v>218.3406894244907</v>
+        <v>160.442118566535</v>
       </c>
       <c r="D5" t="n">
-        <v>107.108674533327</v>
+        <v>106.0042083660494</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.48937768726721</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>211.4419483067483</v>
+        <v>236.7199881956952</v>
       </c>
       <c r="D6" t="n">
-        <v>49.67054334866313</v>
+        <v>65.77120569831082</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.863218273940204</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>160.0769084205552</v>
+        <v>137.3798832460731</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>93.46238144429634</v>
+        <v>65.42366701100744</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
+        <v>25.76596849795754</v>
+      </c>
+      <c r="D10" t="n">
         <v>26.47773558353648</v>
-      </c>
-      <c r="D10" t="n">
-        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.56913593102267</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.486186097780424</v>
+        <v>0.3495021827118645</v>
       </c>
       <c r="C2" t="n">
-        <v>8.379216655746527</v>
+        <v>2.690970457340507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23846688114074</v>
+        <v>6.10647072041516</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.60135367881356</v>
+        <v>3.239767424014474</v>
       </c>
       <c r="C3" t="n">
-        <v>25.70706363570273</v>
+        <v>27.02260555939346</v>
       </c>
       <c r="D3" t="n">
-        <v>70.98526775556563</v>
+        <v>45.32729150507524</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.11246868429443</v>
+        <v>11.65236350170539</v>
       </c>
       <c r="C4" t="n">
-        <v>93.39758609581605</v>
+        <v>58.05761398604363</v>
       </c>
       <c r="D4" t="n">
-        <v>148.6984525283346</v>
+        <v>105.5476956835746</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.89165756629692</v>
+        <v>17.10695374650068</v>
       </c>
       <c r="C5" t="n">
-        <v>206.7315228217722</v>
+        <v>112.6310053697153</v>
       </c>
       <c r="D5" t="n">
-        <v>128.3144249450581</v>
+        <v>109.8084807200058</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.9082651618111</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>272.1414453649201</v>
+        <v>207.7790476222035</v>
       </c>
       <c r="D6" t="n">
-        <v>65.9322123218073</v>
+        <v>69.23284810348508</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>222.1194363381366</v>
+        <v>170.4372919434718</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>143.1142715865788</v>
+        <v>76.77267047210057</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>62.12499472473814</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.418044595559894</v>
+        <v>0.4869468613064179</v>
       </c>
       <c r="C2" t="n">
-        <v>4.625013434706723</v>
+        <v>3.955461500410399</v>
       </c>
       <c r="D2" t="n">
-        <v>9.108655200001905</v>
+        <v>8.71988310912017</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78021168743573</v>
+        <v>2.105848825609408</v>
       </c>
       <c r="C3" t="n">
-        <v>29.05973204570559</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="D3" t="n">
-        <v>66.62630794870978</v>
+        <v>39.93749660876025</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.67929696254333</v>
+        <v>8.767988746628264</v>
       </c>
       <c r="C4" t="n">
-        <v>83.4299016545982</v>
+        <v>63.87741437681872</v>
       </c>
       <c r="D4" t="n">
-        <v>150.0768263050971</v>
+        <v>104.6925934331756</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.53670686571608</v>
+        <v>17.81872083207961</v>
       </c>
       <c r="C5" t="n">
-        <v>200.7183181332604</v>
+        <v>110.8147721168587</v>
       </c>
       <c r="D5" t="n">
-        <v>142.279786037969</v>
+        <v>123.4547738090364</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.19381487502668</v>
+        <v>17.14720540237479</v>
       </c>
       <c r="C6" t="n">
-        <v>303.5779886026073</v>
+        <v>193.2079481957723</v>
       </c>
       <c r="D6" t="n">
-        <v>79.5372720072596</v>
+        <v>87.42659655858698</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>280.2094479984203</v>
+        <v>244.0379355831509</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>182.4185409260998</v>
+        <v>156.2156946997524</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>65.12030697039516</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>18.30272245027328</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.168099841604457</v>
+        <v>0.5713771638716436</v>
       </c>
       <c r="C2" t="n">
-        <v>10.45168605941154</v>
+        <v>4.749695393146069</v>
       </c>
       <c r="D2" t="n">
-        <v>15.49197877301467</v>
+        <v>14.06255411563131</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.66316272645211</v>
+        <v>1.860411899547706</v>
       </c>
       <c r="C3" t="n">
-        <v>24.03809253848316</v>
+        <v>16.01230505626548</v>
       </c>
       <c r="D3" t="n">
-        <v>59.82770509680063</v>
+        <v>37.67947688899258</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.10198825471721</v>
+        <v>6.317546476828225</v>
       </c>
       <c r="C4" t="n">
-        <v>77.63562670413351</v>
+        <v>51.8804574309227</v>
       </c>
       <c r="D4" t="n">
-        <v>148.8388424500419</v>
+        <v>101.348760752511</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.75760009917161</v>
+        <v>15.6834195753428</v>
       </c>
       <c r="C5" t="n">
-        <v>180.2979658849268</v>
+        <v>114.741762933846</v>
       </c>
       <c r="D5" t="n">
-        <v>157.6195939168254</v>
+        <v>133.1495323884737</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.86050368166828</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C6" t="n">
-        <v>313.8019091946335</v>
+        <v>185.3588753003191</v>
       </c>
       <c r="D6" t="n">
-        <v>97.69076880648737</v>
+        <v>104.1310337463464</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.08115056874977</v>
+        <v>14.25301317025519</v>
       </c>
       <c r="C7" t="n">
-        <v>342.2519759160018</v>
+        <v>265.1779088986975</v>
       </c>
       <c r="D7" t="n">
-        <v>51.92169083450106</v>
+        <v>60.06626978893259</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>253.6836067773758</v>
+        <v>242.5849489808656</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>126.8015517328137</v>
+        <v>129.3531140161512</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>52.81311774995717</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.769330347231005</v>
+        <v>3.153373626040755</v>
       </c>
       <c r="C2" t="n">
-        <v>7.007715112913733</v>
+        <v>10.71872143496668</v>
       </c>
       <c r="D2" t="n">
-        <v>7.580074024489623</v>
+        <v>10.6185831691335</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.292380889416302</v>
+        <v>0.5095270585040946</v>
       </c>
       <c r="C2" t="n">
-        <v>6.020076922441441</v>
+        <v>7.726354432422397</v>
       </c>
       <c r="D2" t="n">
-        <v>11.52571804785755</v>
+        <v>14.19705355111313</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.44780012632356</v>
+        <v>1.875138115111408</v>
       </c>
       <c r="C3" t="n">
-        <v>32.47130531796326</v>
+        <v>17.21985473248905</v>
       </c>
       <c r="D3" t="n">
-        <v>65.61510781333557</v>
+        <v>39.5840674352314</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.67777543549135</v>
+        <v>4.900884539600077</v>
       </c>
       <c r="C4" t="n">
-        <v>110.2316139805361</v>
+        <v>45.77987719673301</v>
       </c>
       <c r="D4" t="n">
-        <v>152.5527940152076</v>
+        <v>96.7414187764807</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.36746104549135</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C5" t="n">
-        <v>267.8453174111361</v>
+        <v>105.2924412804704</v>
       </c>
       <c r="D5" t="n">
-        <v>142.6724851196678</v>
+        <v>139.1627370769854</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.28054316370311</v>
+        <v>21.25287430153496</v>
       </c>
       <c r="C6" t="n">
-        <v>283.8546772242889</v>
+        <v>182.984027603746</v>
       </c>
       <c r="D6" t="n">
-        <v>77.60519252530189</v>
+        <v>120.2719477518683</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>178.4022110680261</v>
+        <v>269.8490644755038</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>72.76223110025235</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>93.46238144429634</v>
+        <v>297.1603038599458</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>42.47531442423825</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>207.4531073843934</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>98.22385780989339</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>41.04785326226338</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.6666888066416</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.952737241475911</v>
+        <v>4.287292224445821</v>
       </c>
       <c r="C2" t="n">
-        <v>7.252170291271189</v>
+        <v>6.267477343911637</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1722888743287</v>
+        <v>23.49518605803467</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.13654504634832</v>
+        <v>5.217989048071797</v>
       </c>
       <c r="C3" t="n">
-        <v>17.65673246087889</v>
+        <v>21.16157176504</v>
       </c>
       <c r="D3" t="n">
-        <v>9.503317777109125</v>
+        <v>10.27398972494287</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39867932596747</v>
+        <v>11.677922038805</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14602705947675</v>
+        <v>59.94666646586569</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576315214819702</v>
+        <v>0.7785281359203337</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.561600744558181</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C2" t="n">
-        <v>4.696681017116741</v>
+        <v>6.139850142359552</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30548776693678</v>
+        <v>19.0684856595858</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.41267819314893</v>
+        <v>11.30482481440202</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5927799913826</v>
+        <v>23.40486526924396</v>
       </c>
       <c r="D3" t="n">
-        <v>16.5915362017711</v>
+        <v>28.36759991421159</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.86932974434394</v>
+        <v>6.611089040398021</v>
       </c>
       <c r="C4" t="n">
-        <v>27.43984833369835</v>
+        <v>34.93156506480576</v>
       </c>
       <c r="D4" t="n">
-        <v>20.05023336383261</v>
+        <v>19.62906359871073</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44305641684494</v>
+        <v>13.62806027720508</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15599895713497</v>
+        <v>73.75185561781572</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251169771967357</v>
+        <v>1.603301209082951</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.984333094461056</v>
+        <v>2.137264752145306</v>
       </c>
       <c r="C2" t="n">
-        <v>4.130212591766331</v>
+        <v>6.216426463290803</v>
       </c>
       <c r="D2" t="n">
-        <v>27.18753917370692</v>
+        <v>19.44351328260808</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8986433067511</v>
+        <v>9.675123625352317</v>
       </c>
       <c r="C3" t="n">
-        <v>20.75905520629881</v>
+        <v>23.76320318129405</v>
       </c>
       <c r="D3" t="n">
-        <v>28.98610096788708</v>
+        <v>37.52730599483433</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.23189774684727</v>
+        <v>15.82577299245858</v>
       </c>
       <c r="C4" t="n">
-        <v>47.54113257815179</v>
+        <v>49.62145596345079</v>
       </c>
       <c r="D4" t="n">
-        <v>23.86628669023996</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.84831213192726</v>
+        <v>6.577709618453631</v>
       </c>
       <c r="C5" t="n">
-        <v>31.19503330244241</v>
+        <v>40.71798603363646</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>26.99806186678729</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73778456121089</v>
+        <v>14.83812460359509</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1004858233864</v>
+        <v>87.38006711005995</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021335368363267</v>
+        <v>2.473020767265848</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.723188205131405</v>
+        <v>1.578650308428871</v>
       </c>
       <c r="C2" t="n">
-        <v>5.869869523691679</v>
+        <v>7.444592841303563</v>
       </c>
       <c r="D2" t="n">
-        <v>24.38661297349077</v>
+        <v>15.40263973192821</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.90216938694059</v>
+        <v>8.393942871310228</v>
       </c>
       <c r="C3" t="n">
-        <v>18.0199791114502</v>
+        <v>24.26880324898115</v>
       </c>
       <c r="D3" t="n">
-        <v>43.20180772538089</v>
+        <v>44.37499623195583</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.49839334305466</v>
+        <v>17.72741829558465</v>
       </c>
       <c r="C4" t="n">
-        <v>50.00433756810704</v>
+        <v>54.99456114879357</v>
       </c>
       <c r="D4" t="n">
-        <v>32.53217367562655</v>
+        <v>42.0148747509465</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.20008090968388</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C5" t="n">
-        <v>61.45740628585034</v>
+        <v>70.31767931667781</v>
       </c>
       <c r="D5" t="n">
-        <v>31.26866438026092</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>6.84278149860027</v>
       </c>
       <c r="C6" t="n">
-        <v>31.83905979642831</v>
+        <v>40.6139207769863</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06430989808625</v>
+        <v>16.08087899310538</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8481169541817</v>
+        <v>101.5634462722445</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881641865937619</v>
+        <v>3.385448209074818</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.970989537229101</v>
+        <v>1.98214861487431</v>
       </c>
       <c r="C2" t="n">
-        <v>12.36707583039707</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="D2" t="n">
-        <v>28.80349589489717</v>
+        <v>16.0986988542392</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.06000978314607</v>
+        <v>6.754424205218055</v>
       </c>
       <c r="C3" t="n">
-        <v>19.50241814486289</v>
+        <v>27.22386383876405</v>
       </c>
       <c r="D3" t="n">
-        <v>49.03829782712818</v>
+        <v>46.21086443889737</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.05772749256809</v>
+        <v>17.03823140720339</v>
       </c>
       <c r="C4" t="n">
-        <v>39.15602543617979</v>
+        <v>57.67473238138736</v>
       </c>
       <c r="D4" t="n">
-        <v>40.24085664937251</v>
+        <v>53.70552641311752</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.94206118991621</v>
+        <v>21.18120671912494</v>
       </c>
       <c r="C5" t="n">
-        <v>58.29126993965438</v>
+        <v>87.54735152620933</v>
       </c>
       <c r="D5" t="n">
-        <v>28.69157665661304</v>
+        <v>39.51534509593412</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91449013873929</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>44.84034464376883</v>
+        <v>78.16871570753956</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>21.55917958525995</v>
+        <v>38.98618308334508</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060906399463991</v>
+        <v>17.35094519325592</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19599749497492</v>
+        <v>115.3837855351518</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295679799597993</v>
+        <v>4.337736298313979</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.324999547834699</v>
+        <v>3.036545649235384</v>
       </c>
       <c r="C2" t="n">
-        <v>7.777405313043232</v>
+        <v>5.002986300841745</v>
       </c>
       <c r="D2" t="n">
-        <v>25.01885849502571</v>
+        <v>17.05001237965435</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.68756755033803</v>
+        <v>6.710245558526949</v>
       </c>
       <c r="C3" t="n">
-        <v>38.39615271309275</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="D3" t="n">
-        <v>62.06608986248335</v>
+        <v>47.96819282949916</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.72062817711294</v>
+        <v>14.85580626066273</v>
       </c>
       <c r="C4" t="n">
-        <v>45.43528375254238</v>
+        <v>62.58837964114265</v>
       </c>
       <c r="D4" t="n">
-        <v>57.44500341859361</v>
+        <v>63.5455836527833</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.23782929080177</v>
+        <v>23.53740120931728</v>
       </c>
       <c r="C5" t="n">
-        <v>67.20063035569419</v>
+        <v>97.38937226128361</v>
       </c>
       <c r="D5" t="n">
-        <v>37.62548076525901</v>
+        <v>48.32653074154926</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.33966901013618</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="C6" t="n">
-        <v>73.49952362614172</v>
+        <v>108.719722515996</v>
       </c>
       <c r="D6" t="n">
-        <v>33.08686112852601</v>
+        <v>40.49316580936395</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C7" t="n">
-        <v>47.19064864773568</v>
+        <v>75.33735532849173</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>24.86766934857171</v>
+        <v>38.05254101660637</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.284392154917953</v>
+        <v>18.6425103968335</v>
       </c>
       <c r="C21" t="n">
-        <v>75.57556860727377</v>
+        <v>128.7220955971837</v>
       </c>
       <c r="D21" t="n">
-        <v>6.373843135553209</v>
+        <v>5.326431541952429</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.194427103169874</v>
+        <v>2.635010838198439</v>
       </c>
       <c r="C2" t="n">
-        <v>4.432590884674349</v>
+        <v>3.041454387756618</v>
       </c>
       <c r="D2" t="n">
-        <v>25.66583023212436</v>
+        <v>13.41460063082842</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55503161026472</v>
+        <v>9.552405162321465</v>
       </c>
       <c r="C3" t="n">
-        <v>33.46287049925253</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D3" t="n">
-        <v>67.68168673077511</v>
+        <v>53.97648877948964</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>11.30777005751476</v>
       </c>
       <c r="C4" t="n">
-        <v>75.28728619557515</v>
+        <v>88.26697259342222</v>
       </c>
       <c r="D4" t="n">
-        <v>75.64464235992098</v>
+        <v>59.94649656901449</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="C5" t="n">
-        <v>76.18362184955249</v>
+        <v>64.94261063592651</v>
       </c>
       <c r="D5" t="n">
-        <v>49.40645321622075</v>
+        <v>38.55814108429348</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.40258297866598</v>
+        <v>7.406304680837938</v>
       </c>
       <c r="C6" t="n">
-        <v>92.37755023110364</v>
+        <v>49.59004003691489</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>25.39879485656924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>80.00851090529807</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>45.64635950895544</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495105339830831</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.2568232405757</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495105339830831</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
